--- a/1001-Farsadi/Book1.xlsx
+++ b/1001-Farsadi/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29607"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29614"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Tubitak-Projects\1001-Farsadi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7A363B-6413-4C59-8582-F0FFBC5518E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AABD5AE-29CE-4BEB-BD5F-48AE73BF5A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8595" yWindow="4380" windowWidth="22350" windowHeight="12465" xr2:uid="{31C48086-B64A-405D-92B7-BDC020BBC3B5}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15555" xr2:uid="{31C48086-B64A-405D-92B7-BDC020BBC3B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -501,13 +501,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E0A62A-82F7-4CAA-93AC-5F4F1794DA89}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -535,11 +535,11 @@
         <f t="shared" ref="D2:D3" si="0">B2*C2</f>
         <v>5000</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -553,11 +553,14 @@
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5">
+        <v>1591</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -571,11 +574,14 @@
         <f>B4*C4</f>
         <v>25662</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5">
+        <v>25661.66</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -589,11 +595,14 @@
         <f>B5*C5</f>
         <v>450</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5">
+        <v>485.92</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -607,11 +616,11 @@
         <f t="shared" ref="D6:D9" si="1">B6*C6</f>
         <v>2150</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
@@ -625,11 +634,14 @@
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5">
+        <v>1112</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -643,11 +655,14 @@
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5">
+        <v>2803.85</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -661,60 +676,63 @@
         <f t="shared" si="1"/>
         <v>2850</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5">
+        <v>2803.85</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F14" s="2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" s="2">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F15" s="2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G15" s="2">
         <v>1400</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F16" s="2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G16" s="2">
         <v>25662</v>
       </c>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F17" s="3">
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G17" s="3">
         <v>450</v>
       </c>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F18" s="2">
+    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G18" s="2">
         <v>2150</v>
       </c>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F19" s="3">
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F20" s="2">
+    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G20" s="2">
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F21" s="4">
+    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="4">
         <v>2850</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" xr:uid="{F0767E21-89D6-46EC-A186-FDFFABD081DF}"/>
-    <hyperlink ref="E8" r:id="rId2" xr:uid="{962F4334-6A94-4C8C-BE5B-BD4C89BFB5EB}"/>
-    <hyperlink ref="E7" r:id="rId3" xr:uid="{AE8B3473-7244-4681-9A0A-F3C7A1511C49}"/>
-    <hyperlink ref="E2" r:id="rId4" xr:uid="{2EC2D908-9CE0-4D6D-ACB8-B2EBFF71784B}"/>
-    <hyperlink ref="E3" r:id="rId5" display="https://www.hepsiburada.com/esun-yesil-pla-filament-1-75mm-1-kg-p-HBCV00007UJ979?magaza=Market%20Samm&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=sc:hb-ecom.sr:google.md:shop.op:purchase.cid:23176948726&amp;utm_content=agid:187062614589&amp;wt_gl=cpc.pmax.camp23176948726adgr000000&amp;gad_source=4&amp;gad_campaignid=23176948726&amp;gbraid=0AAAAADOiRoZd4gvbCRf3h2xdQnszm5Zv1&amp;gclid=Cj0KCQiAosrJBhD0ARIsAHebCNqZ9LivCSRfAdH8Mb60BFbkevZ-OPr4rGslJBhtK_h6-MEaQlGiyToaAqW4EALw_wcB" xr:uid="{B99D64C9-F623-437D-BD7C-1318488496B4}"/>
-    <hyperlink ref="E5" r:id="rId6" xr:uid="{A340B54B-BBDE-45CF-8043-2B579ADAD66D}"/>
-    <hyperlink ref="E9" r:id="rId7" xr:uid="{198B1157-8F34-4C16-8B39-C7B267BB3359}"/>
-    <hyperlink ref="E6" r:id="rId8" xr:uid="{C0EFA9D5-D749-48D3-9BD3-BFB996328873}"/>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{F0767E21-89D6-46EC-A186-FDFFABD081DF}"/>
+    <hyperlink ref="F8" r:id="rId2" xr:uid="{962F4334-6A94-4C8C-BE5B-BD4C89BFB5EB}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{AE8B3473-7244-4681-9A0A-F3C7A1511C49}"/>
+    <hyperlink ref="F2" r:id="rId4" xr:uid="{2EC2D908-9CE0-4D6D-ACB8-B2EBFF71784B}"/>
+    <hyperlink ref="F3" r:id="rId5" display="https://www.hepsiburada.com/esun-yesil-pla-filament-1-75mm-1-kg-p-HBCV00007UJ979?magaza=Market%20Samm&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=sc:hb-ecom.sr:google.md:shop.op:purchase.cid:23176948726&amp;utm_content=agid:187062614589&amp;wt_gl=cpc.pmax.camp23176948726adgr000000&amp;gad_source=4&amp;gad_campaignid=23176948726&amp;gbraid=0AAAAADOiRoZd4gvbCRf3h2xdQnszm5Zv1&amp;gclid=Cj0KCQiAosrJBhD0ARIsAHebCNqZ9LivCSRfAdH8Mb60BFbkevZ-OPr4rGslJBhtK_h6-MEaQlGiyToaAqW4EALw_wcB" xr:uid="{B99D64C9-F623-437D-BD7C-1318488496B4}"/>
+    <hyperlink ref="F5" r:id="rId6" xr:uid="{A340B54B-BBDE-45CF-8043-2B579ADAD66D}"/>
+    <hyperlink ref="F9" r:id="rId7" xr:uid="{198B1157-8F34-4C16-8B39-C7B267BB3359}"/>
+    <hyperlink ref="F6" r:id="rId8" xr:uid="{C0EFA9D5-D749-48D3-9BD3-BFB996328873}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
